--- a/apiHirams/resources/templates/SITemplate.xlsx
+++ b/apiHirams/resources/templates/SITemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Program\hirams\apiHirams\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F69C423-DE82-4949-B06E-F5FFADE71236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D40E1B1-8616-4CE7-BD07-CA4E26CC1D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="SI" sheetId="34" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">SI!$A$1:$I$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">SI!$A$1:$I$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -519,7 +519,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -574,9 +574,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -601,6 +598,12 @@
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="240">
@@ -1160,15 +1163,15 @@
     </row>
     <row r="4" spans="2:27" ht="20.25" customHeight="1">
       <c r="B4" s="3"/>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1190,12 +1193,12 @@
     </row>
     <row r="5" spans="2:27" ht="25.5" customHeight="1">
       <c r="B5" s="3"/>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="5"/>
@@ -1220,12 +1223,12 @@
     </row>
     <row r="6" spans="2:27" ht="24" customHeight="1">
       <c r="B6" s="3"/>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="5"/>
@@ -1250,12 +1253,12 @@
     </row>
     <row r="7" spans="2:27" ht="27" customHeight="1">
       <c r="B7" s="3"/>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="5"/>
@@ -1487,11 +1490,11 @@
       <c r="C15" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="23">
         <v>49293</v>
       </c>
@@ -1522,11 +1525,11 @@
     <row r="16" spans="2:27" ht="15" customHeight="1">
       <c r="B16" s="11"/>
       <c r="C16" s="12"/>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="13"/>
       <c r="H16" s="23"/>
       <c r="I16" s="2"/>
@@ -1550,9 +1553,10 @@
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="2:27" ht="17.25" customHeight="1">
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
+      <c r="B17" s="34"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
       <c r="G17" s="2"/>
       <c r="H17" s="23"/>
       <c r="I17" s="2"/>
@@ -1576,9 +1580,9 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="2:27" ht="12.75" customHeight="1">
-      <c r="D18" s="25"/>
+      <c r="D18" s="24"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="25"/>
+      <c r="F18" s="24"/>
       <c r="G18" s="2"/>
       <c r="H18" s="1"/>
       <c r="I18" s="2"/>
@@ -1603,7 +1607,7 @@
     </row>
     <row r="19" spans="2:27" ht="15" customHeight="1">
       <c r="G19" s="1"/>
-      <c r="H19" s="24"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -1626,7 +1630,10 @@
     </row>
     <row r="20" spans="2:27" ht="12.75" customHeight="1">
       <c r="G20" s="9"/>
-      <c r="H20" s="19"/>
+      <c r="H20" s="19">
+        <f>H19/1.12*12%</f>
+        <v>0</v>
+      </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
